--- a/career-magazines/UdyogaSopanam_Log_Apr2025-Sep2026.xlsx
+++ b/career-magazines/UdyogaSopanam_Log_Apr2025-Sep2026.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Log" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Log!$A$1:$Q$26</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Log!$A$1:$Q$30</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,15 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="328">
   <si>
     <t xml:space="preserve">Udyoga Sopanam - Opportunities Log</t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage window: April 2025 - September 2026 (18 months) | Sections logged: scholarships &amp; fellowships, internships, admissions &amp; entrance exams (no government job recruitment, per scope)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compiled: 28 September 2026</t>
+    <t xml:space="preserve">Coverage window: April 2025 - October 2026 (19 months) | Sections logged: scholarships &amp; fellowships, internships, admissions &amp; entrance exams (no government job recruitment, per scope)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled 28 September 2026 | updated 21 October 2026 with the 1-21 October 2026 scrape</t>
   </si>
   <si>
     <t xml:space="preserve">Method &amp; caveats</t>
@@ -891,6 +891,123 @@
   </si>
   <si>
     <t xml:space="preserve">Directly verified item: listed among the latest notifications on the magazine's official website udyogasopanam.com as of 28 September 2026 (Telugu headline: MDI lo PGDM 2026 praveshalu). Specific magazine issue not identified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahatma Jyotiba Phule Overseas Vidya Nidhi (BC and EBC students) 2026-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backward Classes Welfare Department, Government of Telangana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postgraduate and PhD studies abroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC and EBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family income below Rs 5 lakh per annum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age not exceeding 35 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-27 (Fall session)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up to Rs 20 lakh or as per admission letter, plus one-way economy air ticket and visa charges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application deadline extended to 31 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.hindustantimes.com/telugu/telangana/tg-overseas-scholarship-deadline-extended-to-till-october-31st-mahatma-jyothiba-phule-overseas-vidya-nidhi-261791977355284.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deadline extension reported 14-15 Oct 2026 (within window); magazine appearance INFERRED from Udyoga Sopanam's normal AP and Telangana scholarship coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambedkar Overseas Vidya Nidhi (SC students) 2026-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC Development Department, Government of Telangana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not stated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registration on TS ePASS; last date shown as 31 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://telanganaepass.cgg.gov.in/OverseasLinks.do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current-session registration status not clearly shown on the portal; magazine appearance INFERRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telangana Post-Matric Scholarship 2026-27 (SC students)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Welfare Department, Government of Telangana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-matriculation (Class 11 to postgraduate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As per scheme norms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rs 204.40 crore released for 32,976 SC students (state Rs 101.44 crore plus Centre Rs 102.96 crore)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funds released 13 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.deccanchronicle.com/southern-states/telangana/telangana-releases-2044-crore-post-matric-scholarships-for-nearly-33000-sc-students-1995641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fund release reported 13-14 Oct 2026 (within window); magazine appearance INFERRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NSP Post-Matric Scholarship for children of beedi, mine and cine workers 2026-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ministry of Labour and Employment, Government of India (Labour Welfare Organisation, Hyderabad)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class 11 to professional degree courses (post-matric)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workers' monthly income up to Rs 10,000 (beedi and mine) and Rs 8,000 (cine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up to Rs 25,000 per annum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-matric applications till 31 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scholarships.gov.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pib.gov.in/PressReleasePage.aspx?PRID=2273209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheme is specific to Telangana and Andhra Pradesh students; magazine appearance INFERRED</t>
   </si>
 </sst>
 </file>
@@ -977,7 +1094,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1005,6 +1122,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
@@ -1058,20 +1181,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1079,11 +1206,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1095,7 +1222,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1119,6 +1246,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1128,7 +1259,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1147,6 +1278,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1208,7 +1346,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1247,139 +1385,139 @@
   <dimension ref="B2:D23"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="9" t="n">
         <f aca="false">COUNTIF(Log!B2:B300,"Scholarship / Fellowship")</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="9" t="n">
         <f aca="false">COUNTIF(Log!B2:B300,"Internship")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="9" t="n">
         <f aca="false">COUNTIF(Log!B2:B300,"Admission / Entrance Exam")</f>
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="9" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="11" t="n">
         <f aca="false">COUNTA(Log!A2:A300)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1404,1407 +1542,1619 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="38"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="Q5" s="7" t="s">
+      <c r="Q5" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="O6" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="Q6" s="7" t="s">
+      <c r="Q6" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="O7" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="Q7" s="7" t="s">
+      <c r="Q7" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="O8" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Q8" s="7" t="s">
+      <c r="Q8" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="Q9" s="7" t="s">
+      <c r="Q9" s="8" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="Q10" s="8" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="P11" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="Q11" s="7" t="s">
+      <c r="Q11" s="8" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="Q12" s="7" t="s">
+      <c r="Q12" s="8" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="N13" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="P13" s="7" t="s">
+      <c r="P13" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="Q13" s="7" t="s">
+      <c r="Q13" s="8" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="N14" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="O14" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="P14" s="7" t="s">
+      <c r="P14" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="Q14" s="7" t="s">
+      <c r="Q14" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="L15" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="M15" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="O15" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="P15" s="7" t="s">
+      <c r="P15" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="Q15" s="7" t="s">
+      <c r="Q15" s="8" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="N16" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="O16" s="7" t="s">
+      <c r="O16" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="P16" s="7" t="s">
+      <c r="P16" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="Q16" s="7" t="s">
+      <c r="Q16" s="8" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="K17" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="L17" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N17" s="7" t="s">
+      <c r="N17" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="O17" s="7" t="s">
+      <c r="O17" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="P17" s="7" t="s">
+      <c r="P17" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="Q17" s="7" t="s">
+      <c r="Q17" s="8" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="K18" s="7" t="s">
+      <c r="K18" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="L18" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="M18" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N18" s="7" t="s">
+      <c r="N18" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="O18" s="7" t="s">
+      <c r="O18" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="P18" s="7" t="s">
+      <c r="P18" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="Q18" s="7" t="s">
+      <c r="Q18" s="8" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="K19" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="L19" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="M19" s="12" t="s">
+      <c r="M19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N19" s="7" t="s">
+      <c r="N19" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="O19" s="7" t="s">
+      <c r="O19" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="P19" s="7" t="s">
+      <c r="P19" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="Q19" s="7" t="s">
+      <c r="Q19" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="K20" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="L20" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N20" s="7" t="s">
+      <c r="N20" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="O20" s="7" t="s">
+      <c r="O20" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="P20" s="7" t="s">
+      <c r="P20" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="Q20" s="7" t="s">
+      <c r="Q20" s="8" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="K21" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="L21" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="M21" s="12" t="s">
+      <c r="M21" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N21" s="7" t="s">
+      <c r="N21" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="O21" s="7" t="s">
+      <c r="O21" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="P21" s="7" t="s">
+      <c r="P21" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="Q21" s="7" t="s">
+      <c r="Q21" s="8" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="L22" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="N22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="O22" s="7" t="s">
+      <c r="O22" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="P22" s="7" t="s">
+      <c r="P22" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="Q22" s="7" t="s">
+      <c r="Q22" s="8" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="L23" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="M23" s="12" t="s">
+      <c r="M23" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N23" s="7" t="s">
+      <c r="N23" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="O23" s="7" t="s">
+      <c r="O23" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="P23" s="7" t="s">
+      <c r="P23" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="Q23" s="7" t="s">
+      <c r="Q23" s="8" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="K24" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="L24" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="M24" s="12" t="s">
+      <c r="M24" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N24" s="7" t="s">
+      <c r="N24" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="O24" s="7" t="s">
+      <c r="O24" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="P24" s="7" t="s">
+      <c r="P24" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="Q24" s="7" t="s">
+      <c r="Q24" s="8" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="K25" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="L25" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="M25" s="12" t="s">
+      <c r="M25" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N25" s="7" t="s">
+      <c r="N25" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="O25" s="7" t="s">
+      <c r="O25" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="P25" s="7" t="s">
+      <c r="P25" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="Q25" s="7" t="s">
+      <c r="Q25" s="8" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="J26" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="K26" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="L26" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="M26" s="14" t="s">
+      <c r="M26" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="N26" s="7" t="s">
+      <c r="N26" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="O26" s="7" t="s">
+      <c r="O26" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="P26" s="7" t="s">
+      <c r="P26" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="Q26" s="7" t="s">
+      <c r="Q26" s="8" t="s">
         <v>288</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="P30" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q26"/>
+  <autoFilter ref="A1:Q30"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/career-magazines/UdyogaSopanam_Log_Apr2025-Sep2026.xlsx
+++ b/career-magazines/UdyogaSopanam_Log_Apr2025-Sep2026.xlsx
@@ -708,7 +708,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Compiled 28 September 2026 | updated 24 October 2026 with the 1-24 October 2026 scrape</t>
+          <t>Compiled 28 September 2026 | updated 25 October 2026 with the 1-25 October 2026 scrape</t>
         </is>
       </c>
     </row>
@@ -840,10 +840,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B11:D12"/>
     <mergeCell ref="B9:D10"/>
     <mergeCell ref="B7:D8"/>
     <mergeCell ref="B13:D14"/>
+    <mergeCell ref="B11:D12"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="17" min="1" max="1"/>
@@ -3431,89 +3431,344 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Dr. NTR UHS Allied and Healthcare Courses 2026-27 (Competent Authority Quota)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Dr. NTR University of Health Sciences, Vijayawada (Government of Andhra Pradesh)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Intermediate (BiPC/MPC) students for Bachelor of Allied &amp; Healthcare courses (B.OT, B.Optom., BMLS, B.AOTT, B.RT, B.MRIT, B.DTT, B.RTT, B.PA and others)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>All categories (OC/BC/SC/ST fee slabs)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>Boys and girls</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>Minimum 17 years as on 31-12-2026; no upper age limit (born on or after 01-01-2010 not eligible)</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr">
         <is>
           <t>Annual (2026-27 admissions)</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>Admission to Allied &amp; Healthcare degree courses; application fee Rs.2,500 (OC), Rs.2,000 (BC/SC/ST)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="17" t="inlineStr">
         <is>
           <t>Applications 18-10-2026 to 28-10-2026 (5:00 PM)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="17" t="inlineStr">
         <is>
           <t>https://drntr.uhsap.in</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="17" t="inlineStr">
         <is>
           <t>http://drntr.uhsap.in/index/notification/20261017182603827.pdf</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="17" t="inlineStr">
         <is>
           <t>Dr. NTR UHS notification dated 17 October 2026 (AP health-university admissions). Included as Udyoga Sopanam-type AP education/admission coverage; the specific US issue placement was not directly verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Scholarship / Fellowship</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AP Post Matric Scholarship (RTF &amp; MTF) 2026-27 - Jnanabhumi</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Government of Andhra Pradesh (Social Welfare Department) via the Jnanabhumi portal</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Intermediate (Class 11) and above - ITI, Polytechnic, Degree, PG and professional courses</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SC, ST, BC, EBC, Kapu, Minority and Differently Abled</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Boys and girls</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Rs.2.5 lakh annual family income (no family member an income-tax payer; land/vehicle/property caps apply)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Annual (2026-27)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RTF: full tuition/special/other/exam fee to the college; MTF: Rs.10,000 (ITI), Rs.15,000 (Polytechnic), Rs.20,000 (Degree and above) per year</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Application window expected Nov-Dec 2026 (tentative); NSP One-Time Registration (OTR) by 31/10/2026</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>jnanabhumi.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://school.careers360.com/articles/ap-post-matric-scholarship-2026-27 ; https://jnanabhumi.ap.gov.in/</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>New 2026-27 cycle (the log already has AP Jnanabhumi Post-Matric 2025-26). INFERRED from Udyoga Sopanam's normal coverage of AP scholarships; the magazine's own site showed only job-recruitment items in this window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Scholarship / Fellowship</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Muskaan Scholarship Program 2.0 (2026-27)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Valvoline Cummins Private Limited (VCPL), implemented via Buddy4Study</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Class 9, 10, 11 or 12 students</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Children of commercial vehicle drivers (LMV/HMV) and mechanics; also EWS students</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Boys and girls</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Rs.8 lakh annual family income</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Annual (2026-27)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Up to Rs.12,000 (one-time grant); minimum 60% in previous class</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Apply by 30/10/2026</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>buddy4study.com</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://www.telanganapatrika.in/uskaan-scholarship-program-2-vcpl-2026/ ; https://www.buddy4study.com/</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>INFERRED from Udyoga Sopanam's normal coverage of AP/Telangana-relevant scholarships (Andhra Pradesh and Telangana are among the eligible states); reported in the Telugu education press on 20 October 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Admission / Entrance Exam</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>APOSS (Andhra Pradesh Open School Society) 10th &amp; Intermediate Admission 2026-27</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Open School Society (APOSS)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Open SSC (Class 10) and Intermediate (Class 12) programmes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>All categories</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Boys and girls</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Annual (2026-27)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Fees as prescribed by APOSS</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Apply online till 31/10/2026</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>apopenschool.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://www.schools360.in/ap-students/</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>INFERRED from Udyoga Sopanam's normal coverage of AP admissions. Notification first issued 12/06/2026; current deadline 31/10/2026; reported 16 October 2026.</t>
         </is>
       </c>
     </row>

--- a/career-magazines/UdyogaSopanam_Log_Apr2025-Sep2026.xlsx
+++ b/career-magazines/UdyogaSopanam_Log_Apr2025-Sep2026.xlsx
@@ -708,7 +708,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Compiled 28 September 2026 | updated 25 October 2026 with the 1-25 October 2026 scrape</t>
+          <t>Compiled 28 September 2026 | updated 27 October 2026 with the 1-27 October 2026 scrape</t>
         </is>
       </c>
     </row>
@@ -841,9 +841,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B9:D10"/>
+    <mergeCell ref="B11:D12"/>
     <mergeCell ref="B7:D8"/>
     <mergeCell ref="B13:D14"/>
-    <mergeCell ref="B11:D12"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3518,255 +3518,255 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>AP Post Matric Scholarship (RTF &amp; MTF) 2026-27 - Jnanabhumi</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Government of Andhra Pradesh (Social Welfare Department) via the Jnanabhumi portal</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Intermediate (Class 11) and above - ITI, Polytechnic, Degree, PG and professional courses</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>SC, ST, BC, EBC, Kapu, Minority and Differently Abled</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>Boys and girls</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>Rs.2.5 lakh annual family income (no family member an income-tax payer; land/vehicle/property caps apply)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>Annual (2026-27)</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>RTF: full tuition/special/other/exam fee to the college; MTF: Rs.10,000 (ITI), Rs.15,000 (Polytechnic), Rs.20,000 (Degree and above) per year</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>Application window expected Nov-Dec 2026 (tentative); NSP One-Time Registration (OTR) by 31/10/2026</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="17" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="17" t="inlineStr">
         <is>
           <t>jnanabhumi.ap.gov.in</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P32" s="17" t="inlineStr">
         <is>
           <t>https://school.careers360.com/articles/ap-post-matric-scholarship-2026-27 ; https://jnanabhumi.ap.gov.in/</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" s="17" t="inlineStr">
         <is>
           <t>New 2026-27 cycle (the log already has AP Jnanabhumi Post-Matric 2025-26). INFERRED from Udyoga Sopanam's normal coverage of AP scholarships; the magazine's own site showed only job-recruitment items in this window.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Muskaan Scholarship Program 2.0 (2026-27)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Valvoline Cummins Private Limited (VCPL), implemented via Buddy4Study</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>Class 9, 10, 11 or 12 students</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>Children of commercial vehicle drivers (LMV/HMV) and mechanics; also EWS students</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>Boys and girls</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>Rs.8 lakh annual family income</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="17" t="inlineStr">
         <is>
           <t>Annual (2026-27)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="17" t="inlineStr">
         <is>
           <t>Up to Rs.12,000 (one-time grant); minimum 60% in previous class</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>Apply by 30/10/2026</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="17" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="17" t="inlineStr">
         <is>
           <t>buddy4study.com</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="17" t="inlineStr">
         <is>
           <t>https://www.telanganapatrika.in/uskaan-scholarship-program-2-vcpl-2026/ ; https://www.buddy4study.com/</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" s="17" t="inlineStr">
         <is>
           <t>INFERRED from Udyoga Sopanam's normal coverage of AP/Telangana-relevant scholarships (Andhra Pradesh and Telangana are among the eligible states); reported in the Telugu education press on 20 October 2026.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="17" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>APOSS (Andhra Pradesh Open School Society) 10th &amp; Intermediate Admission 2026-27</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Andhra Pradesh Open School Society (APOSS)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>Open SSC (Class 10) and Intermediate (Class 12) programmes</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>All categories</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>Boys and girls</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>Annual (2026-27)</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>Fees as prescribed by APOSS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t>Apply online till 31/10/2026</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="17" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="17" t="inlineStr">
         <is>
           <t>apopenschool.ap.gov.in</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34" s="17" t="inlineStr">
         <is>
           <t>https://www.schools360.in/ap-students/</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" s="17" t="inlineStr">
         <is>
           <t>INFERRED from Udyoga Sopanam's normal coverage of AP admissions. Notification first issued 12/06/2026; current deadline 31/10/2026; reported 16 October 2026.</t>
         </is>

--- a/career-magazines/UdyogaSopanam_Log_Apr2025-Sep2026.xlsx
+++ b/career-magazines/UdyogaSopanam_Log_Apr2025-Sep2026.xlsx
@@ -708,7 +708,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Compiled 28 September 2026 | updated 27 October 2026 with the 1-27 October 2026 scrape</t>
+          <t>Compiled 28 October 2026 | updated 28 October 2026 with the 21-28 October 2026 scrape</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="11" ht="15" customHeight="1" s="18">
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>Status is as of 28 September 2026: green = open now, blue = rolling applications, amber = upcoming, grey = dates to be announced, red = closed. Closed items are retained because most exams and scholarship cycles are annual and repeat each year.</t>
+          <t>Status is as of 28 October 2026: green = open now, blue = rolling applications, amber = upcoming, grey = dates to be announced, red = closed.</t>
         </is>
       </c>
     </row>
@@ -841,9 +841,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B9:D10"/>
-    <mergeCell ref="B11:D12"/>
     <mergeCell ref="B7:D8"/>
     <mergeCell ref="B13:D14"/>
+    <mergeCell ref="B11:D12"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -966,2475 +966,2473 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="18">
-      <c r="A2" s="25" t="n">
+      <c r="A2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>Vidyadhan Scholarship Program 2025 (Andhra Pradesh and Telangana)</t>
         </is>
       </c>
-      <c r="D2" s="25" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>Sarojini Damodaran Foundation</t>
         </is>
       </c>
-      <c r="E2" s="25" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>10th pass students entering Intermediate 1st year; later degree, engineering, medical</t>
         </is>
       </c>
-      <c r="F2" s="25" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>Open to all communities from economically weaker families</t>
         </is>
       </c>
-      <c r="G2" s="25" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H2" s="25" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>Family annual income below Rs 2 lakh</t>
         </is>
       </c>
-      <c r="I2" s="25" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J2" s="25" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>Annual; renewable through graduation</t>
         </is>
       </c>
-      <c r="K2" s="25" t="inlineStr">
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>Rs 10,000 per year for Intermediate; Rs 10,000 to Rs 75,000 per year for degree, engineering and medical courses</t>
         </is>
       </c>
-      <c r="L2" s="25" t="inlineStr">
+      <c r="L2" s="17" t="inlineStr">
         <is>
           <t>Applications closed 30 June 2025; screening test 13 July 2025; interviews 19-31 July 2025</t>
         </is>
       </c>
-      <c r="M2" s="30" t="inlineStr">
+      <c r="M2" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N2" s="25" t="inlineStr">
+      <c r="N2" s="17" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="O2" s="25" t="inlineStr">
+      <c r="O2" s="17" t="inlineStr">
         <is>
           <t>www.vidyadhan.org</t>
         </is>
       </c>
-      <c r="P2" s="25" t="inlineStr">
+      <c r="P2" s="17" t="inlineStr">
         <is>
           <t>https://www.vidyadhan.org/apply</t>
         </is>
       </c>
-      <c r="Q2" s="25" t="inlineStr">
+      <c r="Q2" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; 90 percent (or 9 CGPA) in class 10 required, 75 percent for students with disability. Widely covered in Telugu media (TV9 Telugu, Eenadu) and within the magazine's normal scholarship coverage.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="18">
-      <c r="A3" s="25" t="n">
+      <c r="A3" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Vidyadhan Scholarship 2026 (Andhra Pradesh and Telangana)</t>
         </is>
       </c>
-      <c r="D3" s="25" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Sarojini Damodaran Foundation</t>
         </is>
       </c>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Students who passed class 10 in 2026 entering Intermediate; continuing support through degree</t>
         </is>
       </c>
-      <c r="F3" s="25" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Open to all communities from economically weaker families</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H3" s="25" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>Family annual income below Rs 2 lakh</t>
         </is>
       </c>
-      <c r="I3" s="25" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J3" s="25" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>Annual; renewable through graduation</t>
         </is>
       </c>
-      <c r="K3" s="25" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>Up to Rs 10,000 per year for Inter; up to Rs 75,000 per year for degree, engineering and medical courses</t>
         </is>
       </c>
-      <c r="L3" s="25" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>Applications invited from April 2026; deadline 20 June 2026 (some coverage reported extension to 5 July 2026)</t>
         </is>
       </c>
-      <c r="M3" s="30" t="inlineStr">
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N3" s="25" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="O3" s="25" t="inlineStr">
+      <c r="O3" s="17" t="inlineStr">
         <is>
           <t>www.vidyadhan.org</t>
         </is>
       </c>
-      <c r="P3" s="25" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
         <is>
           <t>https://pratibha.eenadu.net/home/article_landing/education-job-information/the-deadline-for-applying-for-vidyadan-scholarship/9-23010017160</t>
         </is>
       </c>
-      <c r="Q3" s="25" t="inlineStr">
+      <c r="Q3" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; deadline of 20 June 2026 per Eenadu Pratibha (10 May 2026), with later Telugu coverage reporting 5 July 2026 after extension.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
-      <c r="A4" s="25" t="n">
+      <c r="A4" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>PM-USP Central Sector Scheme of Scholarship for College and University Students (CSSS) 2025</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Ministry of Education, Government of India (via National Scholarship Portal)</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>First year UG and integrated PG students (regular courses)</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Open to all; board-exam merit based</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>50 percent of scholarships reserved for girls</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>Income certificate required for fresh applicants</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>18 to 25 years</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>Annual; up to 5 years (UG plus PG)</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Rs 12,000 per year for first 3 years of UG; Rs 20,000 per year at PG level (4th year for professional courses)</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>Apply by 31 October 2025 on National Scholarship Portal</t>
         </is>
       </c>
-      <c r="M4" s="30" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N4" s="25" t="inlineStr">
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="17" t="inlineStr">
         <is>
           <t>www.scholarships.gov.in</t>
         </is>
       </c>
-      <c r="P4" s="25" t="inlineStr">
+      <c r="P4" s="17" t="inlineStr">
         <is>
           <t>https://pratibha.eenadu.net/notifications/notification_article/scholorships/central-sector-scheme-of-scholarship/2-8-31-23070016830</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; details as reported by Eenadu Pratibha notification (July 2025); 82,000 scholarships nationwide each year.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="18">
-      <c r="A5" s="25" t="n">
+      <c r="A5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Telangana ePASS Post-Matric Scholarships 2025-26 (fresh and renewal)</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Government of Telangana (Scheduled Castes Development and other welfare departments)</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>Post-matric courses from ITI to degree and PG</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>SC, ST, BC, EBC, Minority and differently-abled students</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>Category-wise income ceilings apply (about Rs 1 to 2 lakh per year)</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>Annual (academic year 2025-26)</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>Full tuition fee reimbursement plus maintenance allowance; DBT to student accounts</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>Registration opened 1 July 2025; deadline extended repeatedly to 31 March 2026, then 20 April 2026 and finally 31 May 2026</t>
         </is>
       </c>
-      <c r="M5" s="30" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="N5" s="17" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="O5" s="17" t="inlineStr">
         <is>
           <t>telanganaepass.cgg.gov.in</t>
         </is>
       </c>
-      <c r="P5" s="25" t="inlineStr">
+      <c r="P5" s="17" t="inlineStr">
         <is>
           <t>https://www.thehindu.com/news/national/telangana/registration-date-for-post-matric-scholarship-extended/article70787956.ece</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="Q5" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; window verified via The Hindu (26 March 2026) and Telangana government press notes; 75 percent attendance required.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="18">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Andhra Pradesh Jnanabhumi Post-Matric Scholarships 2025-26 (RTF and MTF)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Government of Andhra Pradesh (Social Welfare Department, saturation mode)</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>ITI, Polytechnic, Degree and above level courses</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>SC, ST, BC, EBC, Kapu, Minority and differently-abled students</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H6" s="25" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>Family annual income up to Rs 2.5 lakh (with land and property criteria)</t>
         </is>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>Annual (academic year 2025-26)</t>
         </is>
       </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>RTF full tuition fee reimbursement; MTF Rs 10,000 per year for ITI, Rs 15,000 for Polytechnic, Rs 20,000 for degree and above</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>Applications open with the academic year; completion window roughly August to October 2025</t>
         </is>
       </c>
-      <c r="M6" s="30" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N6" s="25" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="O6" s="25" t="inlineStr">
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t>jnanabhumi.ap.gov.in</t>
         </is>
       </c>
-      <c r="P6" s="25" t="inlineStr">
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>https://jnanabhumi.ap.gov.in/</t>
         </is>
       </c>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="Q6" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; scheme terms verified from the Jnanabhumi official portal; exact 2025-26 closing date not published in a single notice.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>ONGC Merit Scholarship 2025-26</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Oil and Natural Gas Corporation Limited</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>First year BE or BTech, MBBS; PG MBA and MSc Geology or Geophysics (2025-26 joiners)</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>SC, ST, OBC and General-EWS (50 percent of scholarships for women)</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>50 percent reserved for women</t>
         </is>
       </c>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>General and EWS up to Rs 2 lakh; SC and ST up to Rs 4.5 lakh</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Not above 30 years as on 1 August 2025</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Annual; paid for course duration</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>Rs 4,000 per month (Rs 48,000 per year); 2,000 scholarships across India</t>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>Apply by 15 May (2025-26 cycle, as reported April 2026)</t>
         </is>
       </c>
-      <c r="M7" s="30" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N7" s="25" t="inlineStr">
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="17" t="inlineStr">
         <is>
           <t>ongcindia.com</t>
         </is>
       </c>
-      <c r="P7" s="25" t="inlineStr">
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t>https://pratibha.eenadu.net/notifications/notification_article/scholorships/ongc-scholarships-for-ug-pg-students/2-8-31-23070026500</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; details per Eenadu Pratibha scholarship notification; minimum 60 percent marks in qualifying exam.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>uGSOT Scholarship Program 2026</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>upGrad School of Technology</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Class 12 (science) pass students joining BE or BTech Computer Science with GenAI, ML, Quantum Computing and Full Stack specialisations</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Open to all; separate tracks including Girls in Tech, Defence and need-based</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Girls in Tech track for female students</t>
         </is>
       </c>
-      <c r="H8" s="25" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>Not specified (merit and need tracks)</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J8" s="25" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>One-time for 2026 admissions</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Up to 100 percent tuition fee waiver plus hostel support in select cases</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>Apply by 13 August 2026 (online only)</t>
         </is>
       </c>
-      <c r="M8" s="30" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N8" s="25" t="inlineStr">
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="O8" s="25" t="inlineStr">
+      <c r="O8" s="17" t="inlineStr">
         <is>
           <t>www.b4s.in/sen/UGST1</t>
         </is>
       </c>
-      <c r="P8" s="25" t="inlineStr">
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>https://education.sakshi.com/scholarships/education-news/ugsot-scholarship-program-2026-apply-online-news-telugu-196630</t>
         </is>
       </c>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="Q8" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; selection through uGNET entrance plus profile score and seat availability; covered by Sakshi Education.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>IIT Hyderabad SURE (Summer Undergraduate Research Exposure) Internship 2026</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Hyderabad</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>Non-IITH students: 2nd and 3rd year BTech or BDes (all branches), 1st year MSc or MA, 3rd and 4th year integrated BTech-MTech</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>100 of 250 intern slots reserved exclusively for girls</t>
         </is>
       </c>
-      <c r="H9" s="25" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Not specified; must be top 20 percent of class</t>
         </is>
       </c>
-      <c r="J9" s="25" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>Annual summer programme</t>
         </is>
       </c>
-      <c r="K9" s="25" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t>Fellowship Rs 15,000 for two months (Rs 7,500 per month for one month; Rs 10,000 for one-and-a-half months); free hostel, mess at intern cost</t>
         </is>
       </c>
-      <c r="L9" s="25" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>Applications 28 February to 14 March 2026 (extended); internship 15 May to 14 July 2026</t>
         </is>
       </c>
-      <c r="M9" s="30" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N9" s="25" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="O9" s="25" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>www.iith.ac.in</t>
         </is>
       </c>
-      <c r="P9" s="25" t="inlineStr">
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t>https://www.iith.ac.in/news/2026/03/10/Summer-Undergraduate-Research-Exposure/</t>
         </is>
       </c>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="Q9" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified from the official IIT Hyderabad notice; results announced April 2026.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="18">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>NITI Aayog Internship Scheme</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>NITI Aayog, Government of India</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>UG students past 2nd year or 4th semester (85 percent in class 12), PG and research students (70 percent aggregate)</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H10" s="25" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J10" s="25" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>Rolling; 6 weeks to 6 months</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>Unpaid; experience certificate on 75 percent attendance</t>
         </is>
       </c>
-      <c r="L10" s="25" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>Applications accepted online between the 1st and 10th of every month</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="N10" s="25" t="inlineStr">
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>www.niti.gov.in</t>
         </is>
       </c>
-      <c r="P10" s="25" t="inlineStr">
+      <c r="P10" s="17" t="inlineStr">
         <is>
           <t>https://fundaspring.com/blogs/education-headlines-in-india/niti-aayog-internship-2025</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; rolling national scheme; coverage month is nominal (start of the review window) since it recurs every month of the period.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="18">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>AP EAPCET 2025 (Engineering, Agriculture and Pharmacy Common Entrance Test)</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>JNTU Kakinada on behalf of APSCHE</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>First year BE, BTech, BPharm, PharmD and agriculture courses in Andhra Pradesh</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per AP rules</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Minimum 16 years for Engineering and Pharmacy; no upper limit</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>Application fee per category-wise APSCHE slabs; late fees Rs 1,000 to Rs 10,000</t>
         </is>
       </c>
-      <c r="L11" s="25" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>Notification 12 March 2025; apply 15 March to 24 April 2025 without late fee (late windows to 16 May); exams 19-20 May 2025 (Agri and Pharmacy) and 21-27 May 2025 (Engineering)</t>
         </is>
       </c>
-      <c r="M11" s="30" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N11" s="25" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="O11" s="25" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>cets.apsche.ap.gov.in/EAPCET</t>
         </is>
       </c>
-      <c r="P11" s="25" t="inlineStr">
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t>https://cets.apsche.ap.gov.in/EAPCET25/EapcetHomepages/ImportantDates.aspx</t>
         </is>
       </c>
-      <c r="Q11" s="25" t="inlineStr">
+      <c r="Q11" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified from the official APSCHE AP EAPCET 2025 schedule; core CET covered by the magazine every year.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="18">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>TG EAPCET 2025 (Telangana EAPCET, formerly TS EAMCET)</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>JNTU Hyderabad on behalf of TGCHE</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>First year BE, BTech, BPharm, PharmD and agriculture courses in Telangana</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per TG rules</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J12" s="25" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>Registration fee category-wise (approx Rs 500 for SC, ST and PH; Rs 900 for others); late fees Rs 250 to Rs 5,000</t>
         </is>
       </c>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>Notification 20 February 2025; apply 25 February to 4 April 2025 without late fee; exams 29-30 April 2025 (Agri and Pharmacy) and 2-5 May 2025 (Engineering)</t>
         </is>
       </c>
-      <c r="M12" s="30" t="inlineStr">
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N12" s="25" t="inlineStr">
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="O12" s="25" t="inlineStr">
+      <c r="O12" s="17" t="inlineStr">
         <is>
           <t>eapcet.tgche.ac.in</t>
         </is>
       </c>
-      <c r="P12" s="25" t="inlineStr">
+      <c r="P12" s="17" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/education/news/ts-eamcet-2025-notice-out-check-important-dates-exam-schedule-and-more/articleshow/118414962.cms</t>
         </is>
       </c>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="Q12" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified via Times of India report of the official TGCHE notice.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="18">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>AP ECET 2025 (Engineering Common Entrance Test)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>JNTU Anantapur on behalf of APSCHE</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>Lateral entry into 2nd year BE, BTech and BPharm for diploma holders and BSc Mathematics graduates</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per AP rules</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J13" s="25" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t>Registration fee Rs 550; late fees Rs 1,000 to Rs 10,000</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>Notification 10 March 2025; apply 12 March to 7 April 2025 without late fee (late windows to 28 April); exam 6 May 2025</t>
         </is>
       </c>
-      <c r="M13" s="30" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N13" s="25" t="inlineStr">
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="17" t="inlineStr">
         <is>
           <t>cets.apsche.ap.gov.in/ECET</t>
         </is>
       </c>
-      <c r="P13" s="25" t="inlineStr">
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t>https://cets.apsche.ap.gov.in/ECET25/UI/ImportantDates.aspx</t>
         </is>
       </c>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="Q13" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified from the official AP ECET 2025 important dates page.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="18">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>TG ECET 2025 (Telangana Engineering Common Entrance Test)</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Osmania University on behalf of TGCHE</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Lateral entry into 2nd year BE, BTech and BPharm for diploma holders and BSc Mathematics graduates</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per TG rules</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J14" s="25" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K14" s="25" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>Registration fee Rs 500 for SC, ST and PH; Rs 900 for others; late fees Rs 500 and Rs 1,000</t>
         </is>
       </c>
-      <c r="L14" s="25" t="inlineStr">
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>Notification 25 February 2025; apply 3 March to 19 April 2025 without late fee; exam 12 May 2025</t>
         </is>
       </c>
-      <c r="M14" s="30" t="inlineStr">
+      <c r="M14" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N14" s="25" t="inlineStr">
+      <c r="N14" s="17" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="O14" s="25" t="inlineStr">
+      <c r="O14" s="17" t="inlineStr">
         <is>
           <t>ecet.tgche.ac.in</t>
         </is>
       </c>
-      <c r="P14" s="25" t="inlineStr">
+      <c r="P14" s="17" t="inlineStr">
         <is>
           <t>https://education.sakshi.com/en/entrance-exam/education-news/tg-ecet-2025-notification-171597</t>
         </is>
       </c>
-      <c r="Q14" s="25" t="inlineStr">
+      <c r="Q14" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified via Sakshi Education and official TG ECET notification copies.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="18">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>AP ICET 2025 (Integrated Common Entrance Test)</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Andhra University, Visakhapatnam on behalf of APSCHE</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>First year MBA and MCA courses in Andhra Pradesh</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per AP rules</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J15" s="25" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K15" s="25" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>Application fee Rs 650 OC, Rs 600 BC, Rs 550 SC and ST; late fees Rs 1,000 to Rs 10,000</t>
         </is>
       </c>
-      <c r="L15" s="25" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>Notification 11 March 2025; apply 13 March to 9 April 2025 without late fee; exam 7 May 2025; results 21 May 2025</t>
         </is>
       </c>
-      <c r="M15" s="30" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N15" s="25" t="inlineStr">
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="O15" s="25" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>cets.apsche.ap.gov.in/ICET</t>
         </is>
       </c>
-      <c r="P15" s="25" t="inlineStr">
+      <c r="P15" s="17" t="inlineStr">
         <is>
           <t>https://cets.apsche.ap.gov.in/ICET25/ICETHomePages/ImportantDates.aspx</t>
         </is>
       </c>
-      <c r="Q15" s="25" t="inlineStr">
+      <c r="Q15" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified from the official AP ICET 2025 important dates page.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="18">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>TG ICET 2025 (Telangana Integrated Common Entrance Test)</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Mahatma Gandhi University, Nalgonda on behalf of TGCHE</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>First year MBA and MCA courses in Telangana universities and affiliated colleges</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per TG rules</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J16" s="25" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K16" s="25" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t>Registration fee Rs 750 general, Rs 550 for SC, ST and differently-abled; late fees Rs 250 and Rs 500</t>
         </is>
       </c>
-      <c r="L16" s="25" t="inlineStr">
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>Notification 6 March 2025; apply 10 March to 3 May 2025 without late fee; exams 8 and 9 June 2025; results 7 July 2025</t>
         </is>
       </c>
-      <c r="M16" s="30" t="inlineStr">
+      <c r="M16" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N16" s="25" t="inlineStr">
+      <c r="N16" s="17" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="O16" s="25" t="inlineStr">
+      <c r="O16" s="17" t="inlineStr">
         <is>
           <t>icet.tgche.ac.in</t>
         </is>
       </c>
-      <c r="P16" s="25" t="inlineStr">
+      <c r="P16" s="17" t="inlineStr">
         <is>
           <t>https://mguniversity.ac.in/uploads/notifications/Press%20Note%20Release%20of%20Notification%20on%2006032025.pdf</t>
         </is>
       </c>
-      <c r="Q16" s="25" t="inlineStr">
+      <c r="Q16" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified from the MGU official press note for TG ICET 2025.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="18">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>AP LAWCET and AP PGLCET 2025</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Sri Padmavati Mahila Visvavidyalayam, Tirupati on behalf of APSCHE</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>3-year and 5-year LLB and 2-year LLM courses in Andhra Pradesh</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per AP rules</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J17" s="25" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t>Application fee approx Rs 900 OC, Rs 850 BC, Rs 800 SC and ST; late fees Rs 1,000 to Rs 10,000</t>
         </is>
       </c>
-      <c r="L17" s="25" t="inlineStr">
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>Notification 22 March 2025; apply 25 March to 27 April 2025 without late fee; exam 5 June 2025; results 22 June 2025</t>
         </is>
       </c>
-      <c r="M17" s="30" t="inlineStr">
+      <c r="M17" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N17" s="25" t="inlineStr">
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="O17" s="25" t="inlineStr">
+      <c r="O17" s="17" t="inlineStr">
         <is>
           <t>cets.apsche.ap.gov.in/LAWCET</t>
         </is>
       </c>
-      <c r="P17" s="25" t="inlineStr">
+      <c r="P17" s="17" t="inlineStr">
         <is>
           <t>https://cets.apsche.ap.gov.in/LAWCET25/UI/ImportantDates.aspx</t>
         </is>
       </c>
-      <c r="Q17" s="25" t="inlineStr">
+      <c r="Q17" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified from the official AP LAWCET 2025 important dates page.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>TG DOST 2025-26 (Degree Online Services, Telangana)</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Telangana Council of Higher Education</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>UG degree admissions (BA, BSc, BCom, BBA, BCA and related) in Telangana universities and colleges</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per TG rules</t>
         </is>
       </c>
-      <c r="G18" s="25" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J18" s="25" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year); 3 phases</t>
         </is>
       </c>
-      <c r="K18" s="25" t="inlineStr">
+      <c r="K18" s="17" t="inlineStr">
         <is>
           <t>Registration fee Rs 200 phase 1 and Rs 400 phases 2 and 3</t>
         </is>
       </c>
-      <c r="L18" s="25" t="inlineStr">
+      <c r="L18" s="17" t="inlineStr">
         <is>
           <t>Notification 2 May 2025; phase 1 registration 3-21 May 2025; phases 2 and 3 through June; classes commence 30 June 2025</t>
         </is>
       </c>
-      <c r="M18" s="30" t="inlineStr">
+      <c r="M18" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N18" s="25" t="inlineStr">
+      <c r="N18" s="17" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="O18" s="25" t="inlineStr">
+      <c r="O18" s="17" t="inlineStr">
         <is>
           <t>dost.cgg.gov.in</t>
         </is>
       </c>
-      <c r="P18" s="25" t="inlineStr">
+      <c r="P18" s="17" t="inlineStr">
         <is>
           <t>https://education.sakshi.com/en/admissions/education-news/dost-2025-26-notification-released-telangana-degree-admission-schedule-out-dostcgggovin-175699</t>
         </is>
       </c>
-      <c r="Q18" s="25" t="inlineStr">
+      <c r="Q18" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; schedule verified via Sakshi Education and Telangana Today reports of the official DOST notification.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="18">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>AP Degree Admissions 2025 (OAMDC online counselling)</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Andhra Pradesh State Council of Higher Education</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>UG degree admissions (BA, BSc, BCom, BBA, B.Voc, BCA and 5-year integrated PG) in AP degree colleges</t>
         </is>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per AP rules</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I19" s="25" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J19" s="25" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year); phased web counselling</t>
         </is>
       </c>
-      <c r="K19" s="25" t="inlineStr">
+      <c r="K19" s="17" t="inlineStr">
         <is>
           <t>Processing fee approx Rs 400 OC, Rs 300 BC, Rs 200 SC and ST</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
+      <c r="L19" s="17" t="inlineStr">
         <is>
           <t>Notification 20 August 2025; phase 1 registration 20-26 August 2025; phase 2 registration extended to 3 October 2025</t>
         </is>
       </c>
-      <c r="M19" s="30" t="inlineStr">
+      <c r="M19" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N19" s="25" t="inlineStr">
+      <c r="N19" s="17" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
       </c>
-      <c r="O19" s="25" t="inlineStr">
+      <c r="O19" s="17" t="inlineStr">
         <is>
           <t>oamdc.ucanapply.com</t>
         </is>
       </c>
-      <c r="P19" s="25" t="inlineStr">
+      <c r="P19" s="17" t="inlineStr">
         <is>
           <t>https://www.thehindu.com/news/national/andhra-pradesh/apsche-extends-undergraduate-admissions-deadline-to-october-3/article70113987.ece</t>
         </is>
       </c>
-      <c r="Q19" s="25" t="inlineStr">
+      <c r="Q19" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; schedule verified via The Hindu and Sakshi Post reports of the APSCHE OAMDC notification.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="18">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>AP EAPCET 2026 (Engineering, Agriculture and Pharmacy Common Entrance Test)</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>JNTU Kakinada on behalf of APSCHE</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>First year BE, BTech, BPharm, PharmD and agriculture courses in Andhra Pradesh (2026-27)</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per AP rules</t>
         </is>
       </c>
-      <c r="G20" s="25" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I20" s="25" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>Minimum 16 years for Engineering and Pharmacy as on 31 December 2026</t>
         </is>
       </c>
-      <c r="J20" s="25" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>Annual (2026-27 academic year)</t>
         </is>
       </c>
-      <c r="K20" s="25" t="inlineStr">
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>Registration fee Rs 800, Rs 750 BC and Rs 700 SC and ST; late fees Rs 1,000 to Rs 10,000</t>
         </is>
       </c>
-      <c r="L20" s="25" t="inlineStr">
+      <c r="L20" s="17" t="inlineStr">
         <is>
           <t>Notification 3 February 2026; apply 4 February to 7 March 2026 without late fee (extended windows to April); exams 12-15 and 18 May 2026 (Engineering) and 19-20 May 2026 (Agri and Pharmacy)</t>
         </is>
       </c>
-      <c r="M20" s="30" t="inlineStr">
+      <c r="M20" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N20" s="25" t="inlineStr">
+      <c r="N20" s="17" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="O20" s="25" t="inlineStr">
+      <c r="O20" s="17" t="inlineStr">
         <is>
           <t>cets.apsche.ap.gov.in/EAPCET</t>
         </is>
       </c>
-      <c r="P20" s="25" t="inlineStr">
+      <c r="P20" s="17" t="inlineStr">
         <is>
           <t>https://cets.apsche.ap.gov.in/eapcet/EapcetHomepages/ImportantDates.aspx</t>
         </is>
       </c>
-      <c r="Q20" s="25" t="inlineStr">
+      <c r="Q20" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified from the official AP EAPCET 2026 important dates page.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="18">
-      <c r="A21" s="25" t="n">
+      <c r="A21" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>TG EAPCET 2026 (Telangana EAPCET)</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>JNTU Hyderabad on behalf of TGCHE</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>First year BE, BTech, BPharm, PharmD and agriculture courses in Telangana (2026-27)</t>
         </is>
       </c>
-      <c r="F21" s="25" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>Open to all; local reservation per TG rules</t>
         </is>
       </c>
-      <c r="G21" s="25" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H21" s="25" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I21" s="25" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J21" s="25" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>Annual (2026-27 academic year)</t>
         </is>
       </c>
-      <c r="K21" s="25" t="inlineStr">
+      <c r="K21" s="17" t="inlineStr">
         <is>
           <t>Registration fee Rs 500 for SC, ST and PH and Rs 900 for others; late fees Rs 250 to Rs 10,000</t>
         </is>
       </c>
-      <c r="L21" s="25" t="inlineStr">
+      <c r="L21" s="17" t="inlineStr">
         <is>
           <t>Notification 14 February 2026; apply 19 February to 4 April 2026 without late fee (late windows to 2 May); exams 4-5 May 2026 (Agri and Pharmacy) and 9-11 May 2026 (Engineering)</t>
         </is>
       </c>
-      <c r="M21" s="30" t="inlineStr">
+      <c r="M21" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N21" s="25" t="inlineStr">
+      <c r="N21" s="17" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="O21" s="25" t="inlineStr">
+      <c r="O21" s="17" t="inlineStr">
         <is>
           <t>eapcet.tgche.ac.in</t>
         </is>
       </c>
-      <c r="P21" s="25" t="inlineStr">
+      <c r="P21" s="17" t="inlineStr">
         <is>
           <t>https://eapcet.tgche.ac.in/</t>
         </is>
       </c>
-      <c r="Q21" s="25" t="inlineStr">
+      <c r="Q21" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; dates verified from the official TG EAPCET 2026 website and Manabadi coverage.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="18">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>MANUU CSE-RCA Entrance 2025-26 (free Civil Services coaching admission)</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Maulana Azad National Urdu University, Hyderabad</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Graduates (any degree) seeking residential coaching for UPSC Civil Services (Prelims cum Mains)</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>Minorities, SC, ST and Women candidates</t>
         </is>
       </c>
-      <c r="G22" s="25" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>Women explicitly eligible; scheme prioritises minorities, SC and ST</t>
         </is>
       </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I22" s="25" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J22" s="25" t="inlineStr">
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 session); 100 seats</t>
         </is>
       </c>
-      <c r="K22" s="25" t="inlineStr">
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>Entrance exam fee Rs 500; admitted students pay about Rs 12,000 total (tuition Rs 5,000, health insurance Rs 2,000, hostel Rs 4,500); mess extra</t>
         </is>
       </c>
-      <c r="L22" s="25" t="inlineStr">
+      <c r="L22" s="17" t="inlineStr">
         <is>
           <t>Notification 20 June 2025; apply 25 June to 25 July 2025; entrance test 3 August 2025; classes from 1 September 2025</t>
         </is>
       </c>
-      <c r="M22" s="30" t="inlineStr">
+      <c r="M22" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N22" s="25" t="inlineStr">
+      <c r="N22" s="17" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="O22" s="25" t="inlineStr">
+      <c r="O22" s="17" t="inlineStr">
         <is>
           <t>manuu.edu.in</t>
         </is>
       </c>
-      <c r="P22" s="25" t="inlineStr">
+      <c r="P22" s="17" t="inlineStr">
         <is>
           <t>https://manuu.edu.in/sites/default/files/Notification/2025-06/Notification_CSERCAMANUU.pdf</t>
         </is>
       </c>
-      <c r="Q22" s="25" t="inlineStr">
+      <c r="Q22" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; admission via objective plus essay test and interview; verified from the official MANUU notification.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="18">
-      <c r="A23" s="25" t="n">
+      <c r="A23" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>University of Hyderabad PG and M.Tech Admissions 2025-26</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>University of Hyderabad</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>41 PG programmes (MSc, MPA, MFA, MVA, MBA, MTech) for 2025-26</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Open to all; all-India admission</t>
         </is>
       </c>
-      <c r="G23" s="25" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H23" s="25" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J23" s="25" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K23" s="25" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>Application fee approx Rs 300 general with concessions for reserved categories</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>Last date for online applications 9 June 2025; interviews 24-26 June 2025; classes from August 2025; selection via CUET PG 2025 or GATE scores</t>
         </is>
       </c>
-      <c r="M23" s="30" t="inlineStr">
+      <c r="M23" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N23" s="25" t="inlineStr">
+      <c r="N23" s="17" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="O23" s="25" t="inlineStr">
+      <c r="O23" s="17" t="inlineStr">
         <is>
           <t>acad.uohyd.ac.in</t>
         </is>
       </c>
-      <c r="P23" s="25" t="inlineStr">
+      <c r="P23" s="17" t="inlineStr">
         <is>
           <t>https://categories.epratibha.net/Notification/admissions/1/2/253903000751</t>
         </is>
       </c>
-      <c r="Q23" s="25" t="inlineStr">
+      <c r="Q23" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; covered by Eenadu Pratibha notifications portal; within the magazine's university admissions coverage.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="18">
-      <c r="A24" s="25" t="n">
+      <c r="A24" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>NEST 2025 (National Entrance Screening Test)</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>NISER Bhubaneswar and UM-DAE CEBS Mumbai (Department of Atomic Energy)</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>5-year integrated MSc in basic sciences at NISER and UM-DAE CEBS</t>
         </is>
       </c>
-      <c r="F24" s="25" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Open to all; 60 percent in class 12 (55 percent for SC, ST and Divyangjan)</t>
         </is>
       </c>
-      <c r="G24" s="25" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H24" s="25" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>Class 12 passed in 2023, 2024 or 2025</t>
         </is>
       </c>
-      <c r="J24" s="25" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>Annual (2025-26 academic year)</t>
         </is>
       </c>
-      <c r="K24" s="25" t="inlineStr">
+      <c r="K24" s="17" t="inlineStr">
         <is>
           <t>Application fee Rs 1,400 for male UR and OBC; Rs 700 for SC, ST, Divyangjan and all female applicants; selected students get DISHA scholarship Rs 60,000 per year plus Rs 20,000 summer internship grant</t>
         </is>
       </c>
-      <c r="L24" s="25" t="inlineStr">
+      <c r="L24" s="17" t="inlineStr">
         <is>
           <t>Applications 17 February to 9 May 2025; exam 22 June 2025</t>
         </is>
       </c>
-      <c r="M24" s="30" t="inlineStr">
+      <c r="M24" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N24" s="25" t="inlineStr">
+      <c r="N24" s="17" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="O24" s="25" t="inlineStr">
+      <c r="O24" s="17" t="inlineStr">
         <is>
           <t>www.nestexam.in</t>
         </is>
       </c>
-      <c r="P24" s="25" t="inlineStr">
+      <c r="P24" s="17" t="inlineStr">
         <is>
           <t>https://www.biotecnika.org/2025/02/nest-2025-national-entrance-screening-test-official-notification-for-admissions-to-niser-um-dae-cebs/</t>
         </is>
       </c>
-      <c r="Q24" s="25" t="inlineStr">
+      <c r="Q24" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; a national entrance exam within the magazine's coverage scope; verified via Biotechnika reproduction of the official notice.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="18">
-      <c r="A25" s="25" t="n">
+      <c r="A25" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>AIAPGET 2026 (All India AYUSH Post Graduate Entrance Test)</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>National Testing Agency (NTA) on behalf of Ministry of AYUSH</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>PG admissions in Ayurveda, Unani, Siddha and Homoeopathy colleges for 2026-27</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Open to all; all-India test</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I25" s="25" t="inlineStr">
+      <c r="I25" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J25" s="25" t="inlineStr">
+      <c r="J25" s="17" t="inlineStr">
         <is>
           <t>Annual (2026-27 academic year)</t>
         </is>
       </c>
-      <c r="K25" s="25" t="inlineStr">
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>Application fee per NTA category-wise slabs (not stated in verified report)</t>
         </is>
       </c>
-      <c r="L25" s="25" t="inlineStr">
+      <c r="L25" s="17" t="inlineStr">
         <is>
           <t>Apply by 31 July 2026; exam 22 August 2026</t>
         </is>
       </c>
-      <c r="M25" s="30" t="inlineStr">
+      <c r="M25" s="17" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="N25" s="25" t="inlineStr">
+      <c r="N25" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="O25" s="25" t="inlineStr">
+      <c r="O25" s="17" t="inlineStr">
         <is>
           <t>exams.nta.ac.in</t>
         </is>
       </c>
-      <c r="P25" s="25" t="inlineStr">
+      <c r="P25" s="17" t="inlineStr">
         <is>
           <t>https://pratibha.eenadu.net/home/article_landing/education-job-information/common-entrance-tests/9-23010018214</t>
         </is>
       </c>
-      <c r="Q25" s="25" t="inlineStr">
+      <c r="Q25" s="17" t="inlineStr">
         <is>
           <t>Not directly verified in a specific magazine issue; date and deadline per Eenadu Pratibha education desk report (July 2026).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="18">
-      <c r="A26" s="25" t="n">
+      <c r="A26" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Admission / Entrance Exam</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>MDI PGDM 2026 Admissions</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Management Development Institute (MDI)</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Post Graduate Diploma in Management (PGDM) 2026 cycle</t>
         </is>
       </c>
-      <c r="F26" s="25" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="G26" s="25" t="inlineStr">
+      <c r="G26" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="H26" s="25" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
       </c>
-      <c r="I26" s="25" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J26" s="25" t="inlineStr">
+      <c r="J26" s="17" t="inlineStr">
         <is>
           <t>Annual (2026 admission cycle)</t>
         </is>
       </c>
-      <c r="K26" s="25" t="inlineStr">
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>Application fee as per MDI admission notice (not stated on magazine site listing)</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
+      <c r="L26" s="17" t="inlineStr">
         <is>
           <t>Application window as per MDI 2026 admission schedule; specific deadline not stated in the magazine listing</t>
         </is>
       </c>
-      <c r="M26" s="32" t="inlineStr">
+      <c r="M26" s="17" t="inlineStr">
         <is>
           <t>Dates TBA</t>
         </is>
       </c>
-      <c r="N26" s="25" t="inlineStr">
+      <c r="N26" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="O26" s="25" t="inlineStr">
+      <c r="O26" s="17" t="inlineStr">
         <is>
           <t>www.mdi.ac.in</t>
         </is>
       </c>
-      <c r="P26" s="25" t="inlineStr">
+      <c r="P26" s="17" t="inlineStr">
         <is>
           <t>https://www.udyogasopanam.com/</t>
         </is>
       </c>
-      <c r="Q26" s="25" t="inlineStr">
+      <c r="Q26" s="17" t="inlineStr">
         <is>
           <t>Directly verified item: listed among the latest notifications on the magazine's official website udyogasopanam.com as of 28 September 2026 (Telugu headline: MDI lo PGDM 2026 praveshalu). Specific magazine issue not identified.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="18">
-      <c r="A27" s="25" t="n">
+      <c r="A27" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Mahatma Jyotiba Phule Overseas Vidya Nidhi (BC and EBC students) 2026-27</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Backward Classes Welfare Department, Government of Telangana</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>Postgraduate and PhD studies abroad</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>BC and EBC</t>
         </is>
       </c>
-      <c r="G27" s="25" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>Family income below Rs 5 lakh per annum</t>
         </is>
       </c>
-      <c r="I27" s="25" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>Age not exceeding 35 years</t>
         </is>
       </c>
-      <c r="J27" s="25" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
         <is>
           <t>2026-27 (Fall session)</t>
         </is>
       </c>
-      <c r="K27" s="25" t="inlineStr">
+      <c r="K27" s="17" t="inlineStr">
         <is>
           <t>Up to Rs 20 lakh or as per admission letter, plus one-way economy air ticket and visa charges</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
+      <c r="L27" s="17" t="inlineStr">
         <is>
           <t>Application deadline extended to 31 Oct 2026</t>
         </is>
       </c>
-      <c r="M27" s="33" t="inlineStr">
+      <c r="M27" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
-      <c r="N27" s="25" t="inlineStr">
+      <c r="N27" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="O27" s="25" t="inlineStr">
+      <c r="O27" s="17" t="inlineStr">
         <is>
           <t>telanganaepass.cgg.gov.in</t>
         </is>
       </c>
-      <c r="P27" s="25" t="inlineStr">
+      <c r="P27" s="17" t="inlineStr">
         <is>
           <t>https://www.hindustantimes.com/telugu/telangana/tg-overseas-scholarship-deadline-extended-to-till-october-31st-mahatma-jyothiba-phule-overseas-vidya-nidhi-261791977355284.html</t>
         </is>
       </c>
-      <c r="Q27" s="25" t="inlineStr">
+      <c r="Q27" s="17" t="inlineStr">
         <is>
           <t>Deadline extension reported 14-15 Oct 2026 (within window); magazine appearance INFERRED from Udyoga Sopanam's normal AP and Telangana scholarship coverage</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="18">
-      <c r="A28" s="25" t="n">
+      <c r="A28" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Ambedkar Overseas Vidya Nidhi (SC students) 2026-27</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>SC Development Department, Government of Telangana</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Postgraduate and PhD studies abroad</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H28" s="25" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>Family income below Rs 5 lakh per annum</t>
         </is>
       </c>
-      <c r="I28" s="25" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>not stated</t>
         </is>
       </c>
-      <c r="J28" s="25" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>2026-27</t>
         </is>
       </c>
-      <c r="K28" s="25" t="inlineStr">
+      <c r="K28" s="17" t="inlineStr">
         <is>
           <t>Up to Rs 20 lakh or as per admission letter, plus one-way economy air ticket and visa charges</t>
         </is>
       </c>
-      <c r="L28" s="25" t="inlineStr">
+      <c r="L28" s="17" t="inlineStr">
         <is>
           <t>Registration on TS ePASS; last date shown as 31 Oct 2026</t>
         </is>
       </c>
-      <c r="M28" s="32" t="inlineStr">
+      <c r="M28" s="17" t="inlineStr">
         <is>
           <t>Dates TBA</t>
         </is>
       </c>
-      <c r="N28" s="25" t="inlineStr">
+      <c r="N28" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="O28" s="25" t="inlineStr">
+      <c r="O28" s="17" t="inlineStr">
         <is>
           <t>telanganaepass.cgg.gov.in</t>
         </is>
       </c>
-      <c r="P28" s="25" t="inlineStr">
+      <c r="P28" s="17" t="inlineStr">
         <is>
           <t>https://telanganaepass.cgg.gov.in/OverseasLinks.do</t>
         </is>
       </c>
-      <c r="Q28" s="25" t="inlineStr">
+      <c r="Q28" s="17" t="inlineStr">
         <is>
           <t>Current-session registration status not clearly shown on the portal; magazine appearance INFERRED</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="18">
-      <c r="A29" s="25" t="n">
+      <c r="A29" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Telangana Post-Matric Scholarship 2026-27 (SC students)</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Social Welfare Department, Government of Telangana</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Post-matriculation (Class 11 to postgraduate)</t>
         </is>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="G29" s="25" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H29" s="25" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>As per scheme norms</t>
         </is>
       </c>
-      <c r="I29" s="25" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>not stated</t>
         </is>
       </c>
-      <c r="J29" s="25" t="inlineStr">
+      <c r="J29" s="17" t="inlineStr">
         <is>
           <t>2026-27</t>
         </is>
       </c>
-      <c r="K29" s="25" t="inlineStr">
+      <c r="K29" s="17" t="inlineStr">
         <is>
           <t>Rs 204.40 crore released for 32,976 SC students (state Rs 101.44 crore plus Centre Rs 102.96 crore)</t>
         </is>
       </c>
-      <c r="L29" s="25" t="inlineStr">
+      <c r="L29" s="17" t="inlineStr">
         <is>
           <t>Funds released 13 Oct 2026</t>
         </is>
       </c>
-      <c r="M29" s="33" t="inlineStr">
+      <c r="M29" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
-      <c r="N29" s="25" t="inlineStr">
+      <c r="N29" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="O29" s="25" t="inlineStr">
+      <c r="O29" s="17" t="inlineStr">
         <is>
           <t>telanganaepass.cgg.gov.in</t>
         </is>
       </c>
-      <c r="P29" s="25" t="inlineStr">
+      <c r="P29" s="17" t="inlineStr">
         <is>
           <t>https://www.deccanchronicle.com/southern-states/telangana/telangana-releases-2044-crore-post-matric-scholarships-for-nearly-33000-sc-students-1995641</t>
         </is>
       </c>
-      <c r="Q29" s="25" t="inlineStr">
+      <c r="Q29" s="17" t="inlineStr">
         <is>
           <t>Fund release reported 13-14 Oct 2026 (within window); magazine appearance INFERRED</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="18">
-      <c r="A30" s="25" t="n">
+      <c r="A30" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Scholarship / Fellowship</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>NSP Post-Matric Scholarship for children of beedi, mine and cine workers 2026-27</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Ministry of Labour and Employment, Government of India (Labour Welfare Organisation, Hyderabad)</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Class 11 to professional degree courses (post-matric)</t>
         </is>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="G30" s="25" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H30" s="25" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>Workers' monthly income up to Rs 10,000 (beedi and mine) and Rs 8,000 (cine)</t>
         </is>
       </c>
-      <c r="I30" s="25" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>not stated</t>
         </is>
       </c>
-      <c r="J30" s="25" t="inlineStr">
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>2026-27</t>
         </is>
       </c>
-      <c r="K30" s="25" t="inlineStr">
+      <c r="K30" s="17" t="inlineStr">
         <is>
           <t>Up to Rs 25,000 per annum</t>
         </is>
       </c>
-      <c r="L30" s="25" t="inlineStr">
+      <c r="L30" s="17" t="inlineStr">
         <is>
           <t>Post-matric applications till 31 Oct 2026</t>
         </is>
       </c>
-      <c r="M30" s="33" t="inlineStr">
+      <c r="M30" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
-      <c r="N30" s="25" t="inlineStr">
+      <c r="N30" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="O30" s="25" t="inlineStr">
+      <c r="O30" s="17" t="inlineStr">
         <is>
           <t>scholarships.gov.in</t>
         </is>
       </c>
-      <c r="P30" s="25" t="inlineStr">
+      <c r="P30" s="17" t="inlineStr">
         <is>
           <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2273209</t>
         </is>
       </c>
-      <c r="Q30" s="25" t="inlineStr">
+      <c r="Q30" s="17" t="inlineStr">
         <is>
           <t>Scheme is specific to Telangana and Andhra Pradesh students; magazine appearance INFERRED</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A31" s="17" t="n">
+        <v>30</v>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
